--- a/pythonWork/testModels/crmTest/DB/crmTest_MAP.xlsx
+++ b/pythonWork/testModels/crmTest/DB/crmTest_MAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Documents/Projekte/FYAYC_intern/fyyccim-tools/pythonWork/testModels/crmTest/DB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDDF6C9-A510-C049-89CB-77B5477E3CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736EC750-C3C5-0548-87F8-B2A93C72850B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="49740" windowHeight="28300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="203">
   <si>
     <t>System</t>
   </si>
@@ -4607,6 +4607,9 @@
       <c r="C2" t="s">
         <v>81</v>
       </c>
+      <c r="E2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
